--- a/results/Int Task Remove ACC -0.0/Rando_fi_explain.xlsx
+++ b/results/Int Task Remove ACC -0.0/Rando_fi_explain.xlsx
@@ -1148,268 +1148,268 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0001571933772146699</v>
+        <v>0.001108150478686038</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0002140572303170883</v>
+        <v>0.002645961284727451</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001629302516000297</v>
+        <v>0.002687880988531569</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0003893300988531462</v>
+        <v>0.0002935786327348954</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001693334233357645</v>
+        <v>0.003429773967485761</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002840418164189479</v>
+        <v>0.00549511243414935</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0003502753740016729</v>
+        <v>1.381361184254802e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001725987164572274</v>
+        <v>0.0003418861269541935</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02243121975909725</v>
+        <v>0.01888730710312844</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02763832604936799</v>
+        <v>0.02672438008842882</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001916647085441057</v>
+        <v>0.003854160394395877</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0009856081473444162</v>
+        <v>-0.0004397516111831195</v>
       </c>
       <c r="O3" t="n">
-        <v>0.003081397177292196</v>
+        <v>0.003248658167817757</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01308865651742956</v>
+        <v>0.01466337547544874</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.008442834572556488</v>
+        <v>0.007935498037885253</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001007015408679418</v>
+        <v>0.002695775012283875</v>
       </c>
       <c r="S3" t="n">
-        <v>1.248634605380425e-05</v>
+        <v>0.003267280598086865</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0009006336745248936</v>
+        <v>-0.001669708025402029</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0004609363644496557</v>
+        <v>0.003188821148069951</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.000137146382731917</v>
+        <v>0.0001700176547372579</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0053545462824137</v>
+        <v>0.00392616315708858</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.001316872412686567</v>
+        <v>0.0005055835221614618</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0007637230784675552</v>
+        <v>0.000620360242161822</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0003320817382889019</v>
+        <v>2.278679352757202e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.0003311205711154262</v>
+        <v>0.002099095411039159</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0001770230374929421</v>
+        <v>0.0002454646219906337</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.0001183066716663405</v>
+        <v>0.002026438335025249</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.00183735360247389</v>
+        <v>-0.004494124662563982</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.001148010246695063</v>
+        <v>-0.002146412463858465</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.002514073849496807</v>
+        <v>-0.001983214233665018</v>
       </c>
       <c r="AG3" t="n">
-        <v>-8.706327124458178e-05</v>
+        <v>9.30296707784012e-05</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0001067839351639421</v>
+        <v>1.20303649802056e-05</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.001289307479202602</v>
+        <v>-0.0003899695065243653</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.003063243107930527</v>
+        <v>-0.002999873163104883</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0003196796908059052</v>
+        <v>0.0002890808878153528</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.0006160888479597281</v>
+        <v>-0.0002848491658547426</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.0006384614875293692</v>
+        <v>0.0003001119969209722</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.00169821210688665</v>
+        <v>-0.001639608169094428</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.0004912879491111992</v>
+        <v>0.000113600492083818</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.0008698550993155579</v>
+        <v>0.0002016531161033303</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.003282512677194064</v>
+        <v>-0.002729640750278278</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.0005636222421540521</v>
+        <v>0.0003926495307216516</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.0007880856936014374</v>
+        <v>-0.002100274243392903</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.0005442125554168913</v>
+        <v>-0.000650734287738019</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.0001208627199863627</v>
+        <v>0.001428588717274222</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.00139880617820745</v>
+        <v>0.001799861111407311</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.0003054177981865331</v>
+        <v>-0.0004400291212809604</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.0001518680640264752</v>
+        <v>0.001467390286953309</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.001512758031003436</v>
+        <v>-0.004740791772284937</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.003508497876785287</v>
+        <v>-0.0006218457802481106</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.001529246328497452</v>
+        <v>-0.002585549955258846</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.0004983261325984146</v>
+        <v>-0.0004830174675396359</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.0004751502951339142</v>
+        <v>0.0003010932395896682</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.000175474498655786</v>
+        <v>-0.0005929484990367594</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.0007043890522521405</v>
+        <v>-0.002065544613723285</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.0005980078555689255</v>
+        <v>-0.004380180263773801</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.22580645161219e-06</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0.0001390862034799894</v>
+        <v>-0.0002036689520770674</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0.000917395607094517</v>
+        <v>0.001335643466210774</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.301251265678803e-05</v>
+        <v>-0.001220638656401965</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.0002521736581290158</v>
+        <v>-0.0004105472663690186</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.0003051288579967821</v>
+        <v>-0.0003606987617477436</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.002366839167133472</v>
+        <v>-0.003574479343622727</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0.001990828635647708</v>
+        <v>0.001028883767939284</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.001556921700768826</v>
+        <v>0.0003023742613735696</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-6.966540713711056e-05</v>
+        <v>0.0002727945704462803</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0.00199044265821225</v>
+        <v>0.00026829011690599</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.0009271484755363019</v>
+        <v>0.002189410060306312</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.0003575135540388096</v>
+        <v>-0.0007773389728230129</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.003998934076379728</v>
+        <v>0.006438292811587695</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.0006851401773294419</v>
+        <v>-0.0009207444023092521</v>
       </c>
       <c r="BW3" t="n">
-        <v>-0.0007035555239048034</v>
+        <v>0.003807629792680748</v>
       </c>
       <c r="BX3" t="n">
-        <v>4.049453451476059e-05</v>
+        <v>0.0001572259689832834</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.0002243159409986728</v>
+        <v>-0.0006317807054345388</v>
       </c>
       <c r="BZ3" t="n">
-        <v>4.720938207333436e-05</v>
+        <v>1.515465132254591e-05</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.11418685121112e-05</v>
+        <v>-6.529546196538671e-06</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0.0007181434482040171</v>
+        <v>-0.0008199361699761217</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.00092200831776127</v>
+        <v>0.000120122985715998</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.0001674385674492418</v>
+        <v>-5.680882189625035e-05</v>
       </c>
       <c r="CE3" t="n">
-        <v>-9.051037406463513e-05</v>
+        <v>0.0005164056183675958</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.001420716613607884</v>
+        <v>-0.001296625908393074</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.001129982315901625</v>
+        <v>0.0007799582700925367</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.0006525223407384873</v>
+        <v>-0.0003979295173524816</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.002067152498538178</v>
+        <v>0.001175329156413898</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0.001096244272832719</v>
+        <v>0.002272494359705259</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.0003283069099982594</v>
+        <v>-0.0003964643313050469</v>
       </c>
     </row>
     <row r="4">
@@ -1419,268 +1419,268 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003619840347701595</v>
+        <v>0.003084922837070235</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009427155406410443</v>
+        <v>0.008496748661004626</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00659869633818684</v>
+        <v>0.00579940691831519</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005112538009281343</v>
+        <v>0.004319947850632343</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007133842797603257</v>
+        <v>0.007096359218116274</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004290207601237802</v>
+        <v>0.008081448489203349</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0005209690415704106</v>
+        <v>0.0004831237899675498</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005162521700083487</v>
+        <v>0.00535860347693658</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01652554370290955</v>
+        <v>0.01036769569865449</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01649545631028342</v>
+        <v>0.01136803730512041</v>
       </c>
       <c r="M4" t="n">
-        <v>0.007053898941581095</v>
+        <v>0.008613885827535698</v>
       </c>
       <c r="N4" t="n">
-        <v>0.006485341189483491</v>
+        <v>0.003872728813491565</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00745519359285293</v>
+        <v>0.005365878269122106</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01445221905394867</v>
+        <v>0.01778723847345846</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01289644289605556</v>
+        <v>0.01395531026056366</v>
       </c>
       <c r="R4" t="n">
-        <v>0.005230788129562748</v>
+        <v>0.004622305946921959</v>
       </c>
       <c r="S4" t="n">
-        <v>0.004794865719216356</v>
+        <v>0.005734353899093727</v>
       </c>
       <c r="T4" t="n">
-        <v>0.006292373802519403</v>
+        <v>0.00554711412921804</v>
       </c>
       <c r="U4" t="n">
-        <v>0.005825479675085457</v>
+        <v>0.004573669915370255</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0004313484861790714</v>
+        <v>0.0004220442838413166</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0108735470137035</v>
+        <v>0.01255538157460825</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004439512416867641</v>
+        <v>0.005861829915820734</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.004300949268789314</v>
+        <v>0.002576547399515993</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.00198998804888135</v>
+        <v>0.002744574720613775</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002291863135906522</v>
+        <v>0.004009341434426946</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0009485499316048014</v>
+        <v>0.001042338661518762</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.006016123383805746</v>
+        <v>0.008390386016871997</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.00709087146265395</v>
+        <v>0.007105010621171135</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.004742844281970438</v>
+        <v>0.005247866334158599</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.007141584677239576</v>
+        <v>0.007498657180494845</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0008250403497376146</v>
+        <v>0.0007401632007921418</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0008657008458433492</v>
+        <v>0.0008244621164362099</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.004037229369905624</v>
+        <v>0.009721875180318335</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.00468386295128783</v>
+        <v>0.007236968751984888</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.001114497264661272</v>
+        <v>0.002127777759360692</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0008712003456448696</v>
+        <v>0.0005860806258202319</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.0050210432794874</v>
+        <v>0.003637854216211048</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.00359468223535647</v>
+        <v>0.004183779948487538</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0009770940934885144</v>
+        <v>0.001224220556313795</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.003124938481642471</v>
+        <v>0.003565565096567619</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.00638505819588418</v>
+        <v>0.006163769156825582</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.002350705758084984</v>
+        <v>0.005286722269757149</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.003278856045859414</v>
+        <v>0.004776977859005423</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.004317793417391163</v>
+        <v>0.004760089595631225</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.002403886798899719</v>
+        <v>0.003050444834391643</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.00310660786993704</v>
+        <v>0.003657494648373449</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0007054913147185515</v>
+        <v>0.0005606307256954557</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.001856899010880483</v>
+        <v>0.002587433677639002</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.003536136792365369</v>
+        <v>0.007021225474943283</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.00418488924698223</v>
+        <v>0.007100003200268455</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.006273883459715055</v>
+        <v>0.006886894283047408</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.000950479292310477</v>
+        <v>0.001371498559403461</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0007316518036811852</v>
+        <v>0.0009541226609070965</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.0005138198134266998</v>
+        <v>0.001149557503877774</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.004006742881212449</v>
+        <v>0.00338450327811446</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.005571295950329808</v>
+        <v>0.0051132639291647</v>
       </c>
       <c r="BH4" t="n">
-        <v>1.020089567796026e-05</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.001049263089827458</v>
+        <v>0.001137383578056782</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.004650991654580706</v>
+        <v>0.003249379694925298</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.004773837020677638</v>
+        <v>0.006778492111553882</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.001317604580023592</v>
+        <v>0.001211746743136093</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.002672788289335126</v>
+        <v>0.002131199583929206</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.003711098937218576</v>
+        <v>0.009095628001398468</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.004311771680706438</v>
+        <v>0.004503777918814146</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.007155232900433376</v>
+        <v>0.003335406009708053</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0006374074241908095</v>
+        <v>0.0006773542093955314</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.004302676016471836</v>
+        <v>0.006277969624121403</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.004129600351328245</v>
+        <v>0.003464351246168878</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.001247376591290979</v>
+        <v>0.001552023275266093</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.006687499009238318</v>
+        <v>0.008708125346075705</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.002863358159041611</v>
+        <v>0.004025106263493286</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.006840391620427472</v>
+        <v>0.008986399136357619</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0002494379786199615</v>
+        <v>0.0004386575467535654</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.001199991692449166</v>
+        <v>0.001900889435862562</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.001896898867511169</v>
+        <v>0.00135935322563994</v>
       </c>
       <c r="CA4" t="n">
-        <v>9.847923509175034e-05</v>
+        <v>2.064823806835165e-05</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.00245659710060881</v>
+        <v>0.003417858586380445</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.005157799340787728</v>
+        <v>0.002805018607019527</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.0005895090701909005</v>
+        <v>0.0001939473192207645</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.0008331403061422705</v>
+        <v>0.0008040184939004663</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.002413066004372516</v>
+        <v>0.002441725767414087</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.003018618212517072</v>
+        <v>0.004843001111843556</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.001158609103675202</v>
+        <v>0.001632497592427722</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.00529166981914151</v>
+        <v>0.004255602512159075</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.007094080684478411</v>
+        <v>0.007305563463632916</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.002130740707139299</v>
+        <v>0.003495832273919152</v>
       </c>
     </row>
     <row r="5">
@@ -1690,268 +1690,268 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.004967002431399714</v>
+        <v>-0.003737024221453333</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.01886539107082918</v>
+        <v>-0.01785834172541122</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.008962739174219581</v>
+        <v>-0.00393296853625168</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.006912122264675214</v>
+        <v>-0.005105939562348061</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.01104397448808331</v>
+        <v>-0.00762000671366232</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.004411764705882393</v>
+        <v>-0.009097012420275285</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.001387096774193553</v>
+        <v>-0.0007385028533064997</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.009466263846928547</v>
+        <v>-0.008291372943940934</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.009586662035428961</v>
+        <v>0.0008336227856894585</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.001180965613060092</v>
+        <v>0.005419523343127686</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.007433136505731086</v>
+        <v>-0.005175408127822145</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.007854984894259875</v>
+        <v>-0.00748974008207931</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.006277274253105125</v>
+        <v>-0.0007958477508650752</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.004133379645710256</v>
+        <v>-0.01114186851211075</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.00916985064258422</v>
+        <v>-0.007161290322580604</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.006664184661206269</v>
+        <v>-0.004202848211184463</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.007328933657519909</v>
+        <v>-0.003134182174338862</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.008232025008683553</v>
+        <v>-0.007537339353942385</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0105939562348037</v>
+        <v>-0.002987579724739864</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0009032258064516241</v>
+        <v>-0.0003692514266532499</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.006946856547412239</v>
+        <v>-0.01494137353433836</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.007398402222994083</v>
+        <v>-0.008660624370594183</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.004548387096774209</v>
+        <v>-0.003656545870062</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.003166829905321611</v>
+        <v>-0.006301012079660428</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.002651896609600601</v>
+        <v>-0.003726082578046341</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.001548387096774206</v>
+        <v>-0.001074185968445818</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.01067472306143007</v>
+        <v>-0.01242027526015444</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.01476207016325111</v>
+        <v>-0.01584424303457539</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.009100382077110091</v>
+        <v>-0.01013763007720714</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.0105161290322581</v>
+        <v>-0.01527358173883855</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.001215699895797084</v>
+        <v>-0.0006574394463667921</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.0009063444108761698</v>
+        <v>-0.001389371309482457</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.006321639458145167</v>
+        <v>-0.01641935483870963</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.01148036253776439</v>
+        <v>-0.01462618348024808</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.0005035246727089881</v>
+        <v>-0.00294117647058828</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.000622837370242224</v>
+        <v>-0.001215699895797151</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.006425842306356355</v>
+        <v>-0.004309500489715934</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.005244876693296286</v>
+        <v>-0.00708291372943941</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.0006252170892670384</v>
+        <v>-0.001736714136853068</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.005574555403556813</v>
+        <v>-0.006953966699314362</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.01094391244870046</v>
+        <v>-0.0121067031463748</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.005471634776770784</v>
+        <v>-0.009164149043303139</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.00496700243139978</v>
+        <v>-0.0080563947633434</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.00673864482501863</v>
+        <v>-0.01077375122428986</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.0034541723666211</v>
+        <v>-0.003161290322580601</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.007408786299329872</v>
+        <v>-0.005232558139534859</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.001377513030528693</v>
+        <v>-0.001641586867305045</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.001487889273356424</v>
+        <v>-0.002110552763819096</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.003692514266532465</v>
+        <v>-0.01706566347469216</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.0107594936708861</v>
+        <v>-0.008614627285513311</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.0111317944899479</v>
+        <v>-0.01045161290322575</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.002049322681486587</v>
+        <v>-0.002466134074331361</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.001677419354838738</v>
+        <v>-0.001273261508325119</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.000335070737155635</v>
+        <v>-0.002975376196990387</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.004728220402084898</v>
+        <v>-0.006354838709677335</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.00711094564408044</v>
+        <v>-0.0133378932968536</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.001476793248945096</v>
+        <v>-0.002535602639805501</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.006254653760238288</v>
+        <v>-0.004550191038555052</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.004665995300436432</v>
+        <v>-0.007854671280276827</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.002535602639805423</v>
+        <v>-0.002466134074331361</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.002466134074331316</v>
+        <v>-0.00311418685121112</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.007967237527922588</v>
+        <v>-0.01993079584775088</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.006821378340365658</v>
+        <v>-0.007467870788468211</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.01556217423678333</v>
+        <v>-0.004290657439446399</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.0009725599166377274</v>
+        <v>-0.0002978406552494317</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.00944772490448067</v>
+        <v>-0.008788927335640151</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.006903225806451641</v>
+        <v>-0.002318339100346056</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.001860920666013743</v>
+        <v>-0.0029871483153873</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.005882352941176477</v>
+        <v>-0.0114623133032303</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.006903225806451629</v>
+        <v>-0.005941591137965762</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.01556217423678334</v>
+        <v>-0.01036251709986316</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.00034602076124568</v>
+        <v>-0.0001861504095308941</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.002431399791594269</v>
+        <v>-0.004793331017714497</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.004411253907606727</v>
+        <v>-0.002570336922542571</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-6.529546196538671e-05</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.00479333101771443</v>
+        <v>-0.008440430705105972</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.01113179448994789</v>
+        <v>-0.004395218002812895</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.001840916985064223</v>
+        <v>-0.0006042296072507724</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.00145197319434105</v>
+        <v>-0.000415224913494816</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.005505203088284716</v>
+        <v>-0.004828065300451545</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.006180193596425932</v>
+        <v>-0.0074740484429066</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.00258064516129034</v>
+        <v>-0.003548387096774153</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.01023827252419957</v>
+        <v>-0.004430379746835428</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.01589724497393896</v>
+        <v>-0.01118443904133378</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.003473428273706092</v>
+        <v>-0.005314345258770403</v>
       </c>
     </row>
     <row r="6">
@@ -1961,268 +1961,268 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.002083065414629978</v>
+        <v>-0.000314291156556773</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.004202737666565958</v>
+        <v>0.001423112665731627</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0013809718252348</v>
+        <v>-0.0012845242621705</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.00260600370910819</v>
+        <v>-0.002024102836963535</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.001496707221788168</v>
+        <v>-0.0009093952564834668</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0002965927556648929</v>
+        <v>0.002857977022123419</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0006400829311547396</v>
+        <v>-0.0002271789865882057</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.001276187425708861</v>
+        <v>-0.002862901141904595</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01450506416628315</v>
+        <v>0.01759324850056738</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0180037255606938</v>
+        <v>0.02131111938446268</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0009416108215437826</v>
+        <v>-0.001314483811462333</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.003276127110705467</v>
+        <v>-0.002124274256736705</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.001401691036946118</v>
+        <v>-0.0001838289970723217</v>
       </c>
       <c r="P6" t="n">
-        <v>0.00335529492234646</v>
+        <v>0.001173800576344725</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.002013017656232021</v>
+        <v>0.000723820360679192</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.003251840842889505</v>
+        <v>-0.001018778074645113</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.004017826067641986</v>
+        <v>4.653760238273047e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0039247495697454</v>
+        <v>-0.006076410304658587</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.001878161076205809</v>
+        <v>0.0002708036334564415</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0003045227438971343</v>
+        <v>-4.716155217500683e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.004283382874776767</v>
+        <v>-0.005909180500197128</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.004299562280238969</v>
+        <v>-0.002376488812199542</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.001813907775070836</v>
+        <v>-0.0008395486922658831</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0009840219856773469</v>
+        <v>-0.001085679340156201</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.001872528285939448</v>
+        <v>-0.0004621003388718514</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0002566713806860771</v>
+        <v>-0.000538216124158833</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.001906832563076535</v>
+        <v>-0.001827520822871359</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.005137425706637636</v>
+        <v>-0.009360068915701477</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.005340890802285381</v>
+        <v>-0.005448717872570297</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.007150650232941129</v>
+        <v>-0.006951954900489788</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0005572467259428088</v>
+        <v>-0.0004229750972118571</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0004039547186517584</v>
+        <v>-0.0005770662695457507</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.004363513128148799</v>
+        <v>-0.006101332202000578</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.006647402211789508</v>
+        <v>-0.008111364476657928</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0002475426275083043</v>
+        <v>-0.0004800973959082328</v>
       </c>
       <c r="AM6" t="n">
-        <v>8.75837640922139e-05</v>
+        <v>-0.0006868756400286918</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.002038599513988726</v>
+        <v>-0.002986423999135829</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.003934050806074582</v>
+        <v>-0.00482360146998771</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.0001861504095308872</v>
+        <v>-0.0009187653283356384</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.003343788425716235</v>
+        <v>-0.001990563041604235</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.009711460860375196</v>
+        <v>-0.005742113866184529</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.0009695333829734185</v>
+        <v>-0.0003116834607214486</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.003946753572586009</v>
+        <v>-0.004569385209624191</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.002241373327540886</v>
+        <v>-0.0007489960725475114</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.001704041719687381</v>
+        <v>-0.0007145485952788841</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.002353247655435875</v>
+        <v>0.001358535904722012</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.000714083237215557</v>
+        <v>-0.0005667484855401444</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.001285168461271241</v>
+        <v>-0.0002647895970532416</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.001000876708380399</v>
+        <v>-0.009838972268243262</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.006238539706131821</v>
+        <v>-0.005000075908242127</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.0002223808634465696</v>
+        <v>-0.007228973180872747</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.001230757242549682</v>
+        <v>-0.001799033619164222</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.001016591482333109</v>
+        <v>0.0001973901832918096</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.0002074806125102302</v>
+        <v>-0.0004907197276706104</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.003723831693217439</v>
+        <v>-0.003906143465620393</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.001974076977662228</v>
+        <v>-0.007575110548929026</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.0009546308971660922</v>
+        <v>-0.0007092205879234675</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.0051815637176271</v>
+        <v>7.51744624431172e-05</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.003386896008960163</v>
+        <v>-0.005379214067769278</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0001946288071347918</v>
+        <v>-0.001228075618433001</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.001474709289174157</v>
+        <v>-0.001933365969724349</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.00465665302277235</v>
+        <v>-0.008442744371893577</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.005294988350587286</v>
+        <v>-0.0001145741622409602</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.003330509646213442</v>
+        <v>-0.001116361322273963</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0.0002706234404146246</v>
+        <v>-0.0001451612903225402</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.005103187039342105</v>
+        <v>-0.002810354099445668</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.001172747580044676</v>
+        <v>0.000435113667827991</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.0004639690730575186</v>
+        <v>-0.00211901216182672</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.001094093376285274</v>
+        <v>0.001972034538793307</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.001501026214644427</v>
+        <v>-0.003553891360127243</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.003201261440946845</v>
+        <v>-0.0005983093162804543</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.0001571936791594356</v>
+        <v>-8.113057676181756e-05</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.0003021148036254057</v>
+        <v>-0.0009851640125220413</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.0005655709813529086</v>
+        <v>-0.0001929912339965811</v>
       </c>
       <c r="CA6" t="n">
         <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.0009408534674678725</v>
+        <v>-0.0009974096926262915</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.002635131403696875</v>
+        <v>-0.002201350503124414</v>
       </c>
       <c r="CD6" t="n">
         <v>0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.00048868230820589</v>
+        <v>-6.078499478985312e-05</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.002846492498476574</v>
+        <v>-0.003353013162127447</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.002733573506062173</v>
+        <v>-0.001133231837500481</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.00131878341163415</v>
+        <v>-0.001380180361452779</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.00493005368790346</v>
+        <v>-0.002109187556879258</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0.002069350725499886</v>
+        <v>-0.001573741101203252</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.001253317020764658</v>
+        <v>-0.003152146934723217</v>
       </c>
     </row>
     <row r="7">
@@ -2232,268 +2232,268 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.128669298126826e-05</v>
+        <v>0.001360834312254966</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001004178042525039</v>
+        <v>0.003902571867816501</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.047858905287249e-05</v>
+        <v>0.0006824135645262408</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001190799284750094</v>
+        <v>-0.000533570375410597</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001649878430010454</v>
+        <v>0.001717958826053334</v>
       </c>
       <c r="H7" t="n">
-        <v>0.003556005835629777</v>
+        <v>0.004821848766982056</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0003270356261603047</v>
+        <v>-8.561717868035278e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.003846155466388618</v>
+        <v>0.00151970425541374</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02112368022816415</v>
+        <v>0.01871124271512161</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02548164246944085</v>
+        <v>0.02899553391808159</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0007658824688610455</v>
+        <v>0.001547437032268462</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001717544178041486</v>
+        <v>-0.0006541032460790214</v>
       </c>
       <c r="O7" t="n">
-        <v>0.000458929620273843</v>
+        <v>0.001559300828823667</v>
       </c>
       <c r="P7" t="n">
-        <v>0.009485618346323119</v>
+        <v>0.01355286197594376</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.007432391341188027</v>
+        <v>0.007276072007358405</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002392038277419956</v>
+        <v>0.002897557182080329</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0001915060119402124</v>
+        <v>0.001162606922097836</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0004824580614077256</v>
+        <v>-0.003245531971228061</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0002520171460145937</v>
+        <v>0.003230288294546702</v>
       </c>
       <c r="V7" t="n">
-        <v>-5.086797888944617e-05</v>
+        <v>0.0001167810714792772</v>
       </c>
       <c r="W7" t="n">
-        <v>0.004864718535714107</v>
+        <v>0.005562545704566624</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.001449103071182861</v>
+        <v>-3.619591296430131e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>-8.381445574856539e-05</v>
+        <v>0.0006887378066804562</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0001733342131580051</v>
+        <v>1.904794888224758e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.001315999730001893</v>
+        <v>0.001494729218636853</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.983581271416192e-06</v>
+        <v>0.0003027871974958352</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.001208378094636486</v>
+        <v>0.001490589452996122</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.0007449369110225757</v>
+        <v>-0.003996971496017343</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.0004083179208800498</v>
+        <v>-0.003163262549305645</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.004570709180256255</v>
+        <v>-0.001212394730484839</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.0003271665096536258</v>
+        <v>-0.0001364702405160123</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.000106315685318259</v>
+        <v>1.983403180074727e-05</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.001452429563086965</v>
+        <v>0.002407372875240807</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.001603448527586754</v>
+        <v>-0.002568684339886385</v>
       </c>
       <c r="AL7" t="n">
-        <v>-3.53754746652113e-05</v>
+        <v>-3.553611723935423e-05</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.0006952684462145308</v>
+        <v>-0.0003254160073725088</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.0002758700328959806</v>
+        <v>7.479686997985424e-06</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.002855178984619561</v>
+        <v>-0.001854978961120474</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.0004137738586895756</v>
+        <v>0.0001973069617135142</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0002839497770715127</v>
+        <v>0.001015329524422637</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.002442733505937217</v>
+        <v>-0.002512352304181004</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.0007626999474779017</v>
+        <v>0.001823851291542616</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.855676230616438e-05</v>
+        <v>-0.003535962542060583</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.0003102766021872872</v>
+        <v>-0.0001820137337635169</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.0003226727548618191</v>
+        <v>0.001330970859770836</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.001213370116741358</v>
+        <v>0.002054064273547779</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.0003699890087461355</v>
+        <v>-0.0003837010108088623</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.0004194495685176436</v>
+        <v>0.001118336428153055</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.001268663713685025</v>
+        <v>-0.004648668399613698</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0.002967396246297938</v>
+        <v>-0.001656215524469301</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.001767552888616358</v>
+        <v>-0.005047442651323092</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0.0002615757737415403</v>
+        <v>-6.236394425256364e-05</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.0004547507426587328</v>
+        <v>0.0003370990426932064</v>
       </c>
       <c r="BE7" t="n">
-        <v>-5.551115123125783e-18</v>
+        <v>-6.780947500518719e-05</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.001006880660435427</v>
+        <v>-0.002115621049715116</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.0002019910204039022</v>
+        <v>-0.004389929696053053</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0.0002606105733432479</v>
+        <v>-3.660477045292486e-05</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-0.001048151800020164</v>
+        <v>0.001214118200864428</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.001507239513912356</v>
+        <v>-0.002451874053349257</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0005342111400886251</v>
+        <v>-0.0002985266212746862</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.0006069245016111224</v>
+        <v>-0.000872236307418267</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0.003450574557919129</v>
+        <v>0.0004597509762762741</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0.002731440322843531</v>
+        <v>0.001150116681419505</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0005021414558526005</v>
+        <v>4.077467000184739e-05</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0.0001075535699511854</v>
+        <v>8.670350023015638e-05</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0.0006933895921237721</v>
+        <v>-0.0004860126801514208</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0008479716666454085</v>
+        <v>0.001830278865323215</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0003053618728011631</v>
+        <v>-0.0005979823861696099</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.003917613165576745</v>
+        <v>0.006698206007453033</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.0003542772099673186</v>
+        <v>-0.001319696903333193</v>
       </c>
       <c r="BW7" t="n">
-        <v>-0.0001984003989359828</v>
+        <v>0.002205626953803402</v>
       </c>
       <c r="BX7" t="n">
-        <v>5.105814822840559e-05</v>
+        <v>3.51189584298861e-05</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0004633057053190559</v>
+        <v>-0.0004379127458853799</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.172715045142714e-05</v>
+        <v>0.0001501137267644559</v>
       </c>
       <c r="CA7" t="n">
         <v>0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0.0004324200902970365</v>
+        <v>-0.0001643436439002721</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0008776841815676506</v>
+        <v>0.0008029425601519813</v>
       </c>
       <c r="CD7" t="n">
         <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.0001042028482111601</v>
+        <v>0.0003539919671005642</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0.001225010082387545</v>
+        <v>-0.001493195649371465</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.0001708929153298844</v>
+        <v>0.000350489004160609</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.0008734726611109911</v>
+        <v>-0.0003119475115710924</v>
       </c>
       <c r="CI7" t="n">
-        <v>-0.00207086234394932</v>
+        <v>0.001720408450551741</v>
       </c>
       <c r="CJ7" t="n">
-        <v>5.038620426738305e-05</v>
+        <v>0.005784858002246252</v>
       </c>
       <c r="CK7" t="n">
-        <v>-0.0007984643219628661</v>
+        <v>-0.0008768467481583386</v>
       </c>
     </row>
     <row r="8">
@@ -2503,268 +2503,268 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002892906812485079</v>
+        <v>0.001935237672039035</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003253630292776385</v>
+        <v>0.00575398092899074</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003475551650258546</v>
+        <v>0.007087706464813538</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003440278568612833</v>
+        <v>0.0011631544820879</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00603546454684187</v>
+        <v>0.008370494347275603</v>
       </c>
       <c r="H8" t="n">
-        <v>0.006385224829363367</v>
+        <v>0.01023686316976169</v>
       </c>
       <c r="I8" t="n">
-        <v>7.25955416197327e-05</v>
+        <v>0.000364709968739127</v>
       </c>
       <c r="J8" t="n">
-        <v>0.004997614655556287</v>
+        <v>0.003385381035113566</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03183051402008147</v>
+        <v>0.02114968342145359</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03861750863848017</v>
+        <v>0.0353117541933243</v>
       </c>
       <c r="M8" t="n">
-        <v>0.003942114205021816</v>
+        <v>0.006410472713311878</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003373254659532348</v>
+        <v>0.001230758888054803</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01032617774233688</v>
+        <v>0.002875952065526171</v>
       </c>
       <c r="P8" t="n">
-        <v>0.02130070925164426</v>
+        <v>0.02548913075795939</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0181432011860488</v>
+        <v>0.01071293031026958</v>
       </c>
       <c r="R8" t="n">
-        <v>0.004323699791809221</v>
+        <v>0.006061633800110523</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002912338378712303</v>
+        <v>0.006164869707185754</v>
       </c>
       <c r="T8" t="n">
-        <v>0.00562917213745161</v>
+        <v>0.001978892328120272</v>
       </c>
       <c r="U8" t="n">
-        <v>0.002558963053912228</v>
+        <v>0.006636995638212154</v>
       </c>
       <c r="V8" t="n">
-        <v>1.755947921494028e-05</v>
+        <v>0.0002510303101687317</v>
       </c>
       <c r="W8" t="n">
-        <v>0.009934038956691307</v>
+        <v>0.01168631368949738</v>
       </c>
       <c r="X8" t="n">
-        <v>0.00228343722833581</v>
+        <v>0.001809016130408578</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001595029062398562</v>
+        <v>0.002658229863025294</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001700657787991111</v>
+        <v>0.002234643682547779</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0009291845617939859</v>
+        <v>0.005001571836212484</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0006428485390456401</v>
+        <v>0.000826459779501873</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.002313959090709986</v>
+        <v>0.0088805060371133</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.001793723446191559</v>
+        <v>0.001900324345792356</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.001965794614088648</v>
+        <v>0.002815866797257638</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.000209962643777184</v>
+        <v>0.002423294806122951</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0005505009595302923</v>
+        <v>0.0002851005027356218</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0004546615525809816</v>
+        <v>0.0007680773645909411</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0003347950985748472</v>
+        <v>0.006222222071022826</v>
       </c>
       <c r="AK8" t="n">
-        <v>-2.449975503040212e-05</v>
+        <v>0.001089689383750794</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.000409073809854621</v>
+        <v>0.000474827615058665</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.000991198780938729</v>
+        <v>1.517827776051361e-05</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.003212820156144067</v>
+        <v>0.003463496505176228</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.001455645717297788</v>
+        <v>0.0008255331606710991</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0008781172953032962</v>
+        <v>0.001175808597980693</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.001144430616670286</v>
+        <v>0.002650795950343352</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.001929478616712299</v>
+        <v>0.0006726909112982792</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.0006361714859775214</v>
+        <v>0.002199547234165233</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.002298506856760629</v>
+        <v>0.0008336227856894585</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.003572150390538798</v>
+        <v>-3.356831151395678e-05</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0008616604528016353</v>
+        <v>0.003138854325590684</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0.0002572591987659412</v>
+        <v>0.003769233199582991</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.0001201125255508112</v>
+        <v>-0.0002234408953446454</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.0008716707213042019</v>
+        <v>0.0034229976915472</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.003740076852570343</v>
+        <v>0.001675929142063204</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0.0003332610338599079</v>
+        <v>0.001127978374223493</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.005526657925499973</v>
+        <v>0.001177192242971667</v>
       </c>
       <c r="BC8" t="n">
-        <v>-2.448579823705332e-05</v>
+        <v>0.0003796330373461887</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.481847697515698e-05</v>
+        <v>0.0008258508168718148</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.0004475907230716836</v>
+        <v>2.792256142963578e-05</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.448579823702002e-05</v>
+        <v>-0.001401797065378327</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.001726477123373069</v>
+        <v>-0.0008760419794040381</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0006665313105718134</v>
+        <v>0.0005046880232169232</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.00194472628508999</v>
+        <v>0.003351741540498081</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.00102677507612195</v>
+        <v>-0.0001272787589649271</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.001209549528188675</v>
+        <v>1.01410347131653e-05</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.002185691762764189</v>
+        <v>0.001123663920447741</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.001404642386759017</v>
+        <v>0.001326805350297705</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.0004807773774947289</v>
+        <v>0.001809278563746196</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.002341536039619488</v>
+        <v>0.001695164899908139</v>
       </c>
       <c r="BQ8" t="n">
-        <v>-3.284406741825841e-05</v>
+        <v>0.0003553626308836821</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.001059626985052264</v>
+        <v>0.004162380153633763</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.003171772194422643</v>
+        <v>0.002699302084604951</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.001210129508711472</v>
+        <v>0.0002866741771948206</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.009260879093816451</v>
+        <v>0.0120661028345466</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.0006250076363059187</v>
+        <v>-0.0007277034594196568</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.001934038656722975</v>
+        <v>0.007713396320768409</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0002613203854560514</v>
+        <v>0.0001859155128667328</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0007925559693380934</v>
+        <v>0.000338836001070944</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.001362572667257853</v>
+        <v>0.0003084010622033173</v>
       </c>
       <c r="CA8" t="n">
         <v>0</v>
       </c>
       <c r="CB8" t="n">
-        <v>6.90029773879386e-05</v>
+        <v>0.0003531114648961956</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.002331415466323286</v>
+        <v>0.002253125540127929</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>2.517623363541832e-05</v>
+        <v>0.001045169589155365</v>
       </c>
       <c r="CF8" t="n">
-        <v>-0.0003300092998240772</v>
+        <v>0.0004146668154928395</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0008933494303414502</v>
+        <v>0.001929047105387505</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.0001040422056370532</v>
+        <v>0.0006260479446899934</v>
       </c>
       <c r="CI8" t="n">
-        <v>-0.0007665701927357882</v>
+        <v>0.003073984022229922</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.002148091304833111</v>
+        <v>0.007532618633523322</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0008232293698634597</v>
+        <v>0.002113357111269989</v>
       </c>
     </row>
     <row r="9">
@@ -2774,268 +2774,268 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.005996649916247954</v>
+        <v>0.006834170854271349</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01527913809990203</v>
+        <v>0.01570934256055362</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01413646751550763</v>
+        <v>0.01299379693111333</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009141364675155051</v>
+        <v>0.009768378650553865</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01149078726968182</v>
+        <v>0.01632386549134838</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00825987593862223</v>
+        <v>0.02035483870967747</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0002812939521800395</v>
+        <v>0.0008304498269896321</v>
       </c>
       <c r="J9" t="n">
-        <v>0.008036935704514326</v>
+        <v>0.008652530779753798</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04871972318339098</v>
+        <v>0.0411418685121107</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05501730103806226</v>
+        <v>0.04071836186639811</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01900097943192946</v>
+        <v>0.02559582109043427</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01472412667319618</v>
+        <v>0.006934673366834165</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01364675155076719</v>
+        <v>0.01550767221678096</v>
       </c>
       <c r="P9" t="n">
-        <v>0.04247538677918428</v>
+        <v>0.0476441631504923</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02957102672292551</v>
+        <v>0.04201828410689173</v>
       </c>
       <c r="R9" t="n">
-        <v>0.009106891701828445</v>
+        <v>0.00938023450586265</v>
       </c>
       <c r="S9" t="n">
-        <v>0.00658972449739389</v>
+        <v>0.01409677419354844</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01070845576232448</v>
+        <v>0.009270290394638881</v>
       </c>
       <c r="U9" t="n">
-        <v>0.008107202680067071</v>
+        <v>0.01058064516129037</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0005813953488371992</v>
+        <v>0.001161290322580699</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02520404831864182</v>
+        <v>0.02357166176950706</v>
       </c>
       <c r="X9" t="n">
-        <v>0.005051903114186818</v>
+        <v>0.01413646751550769</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0108413132694938</v>
+        <v>0.004395218002812984</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003625170998631999</v>
+        <v>0.002806451612903283</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003935483870967727</v>
+        <v>0.009161290322580706</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.002043551088777274</v>
+        <v>0.002222994095171915</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.0113233761722821</v>
+        <v>0.01393548387096779</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.00976167156382628</v>
+        <v>0.004272316776658569</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.004411253907606838</v>
+        <v>0.004988830975428155</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.01121917332407091</v>
+        <v>0.007849947898575859</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001105527638190984</v>
+        <v>0.001580645161290362</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.001695501730103788</v>
+        <v>0.0009688581314879041</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.006530045154567598</v>
+        <v>0.01446366782006919</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.003651591289782285</v>
+        <v>0.009642591213700685</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.003248974008207906</v>
+        <v>0.004129032258064547</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.002017783857729105</v>
+        <v>0.0008387096774194025</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.01099999999999995</v>
+        <v>0.005696422368878074</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.006627489389487396</v>
+        <v>0.005904828065300449</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.002570336922542549</v>
+        <v>0.001709677419354883</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.003564013840830394</v>
+        <v>0.003909158600148938</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.006007182500816177</v>
+        <v>0.007855547282204039</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.003350083752093869</v>
+        <v>0.007946554149085839</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.002707454289732803</v>
+        <v>0.006709677419354909</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.007236180904522671</v>
+        <v>0.00596314907872697</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.004676511954993012</v>
+        <v>0.007606921318968373</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.004589614740368564</v>
+        <v>0.007780479333101775</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.001161290322580621</v>
+        <v>0.000451545675581766</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.004411764705882326</v>
+        <v>0.00573343261355177</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.006767169179229526</v>
+        <v>0.004020100502512558</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.001742043551088812</v>
+        <v>0.01670718999652655</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.008857242097950723</v>
+        <v>0.01139284473775617</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.001005025125628178</v>
+        <v>0.001407035175879412</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0006574394463667921</v>
+        <v>0.001910385550538385</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.001072664359861608</v>
+        <v>0.0003126085446335303</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.008614102118791312</v>
+        <v>0.005203938115330542</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.01211230819458043</v>
+        <v>0.002215189873417767</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.22580645161219e-05</v>
+        <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.001504787961696286</v>
+        <v>0.001207966046359832</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.006089965397923858</v>
+        <v>0.006912122264675224</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.01003820771101083</v>
+        <v>0.01597777005904828</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.001774193548387082</v>
+        <v>0.001373534338358484</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.004612903225806431</v>
+        <v>0.003199718706047861</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.002500868357068487</v>
+        <v>0.008822507815213609</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.006143001007049287</v>
+        <v>0.009435194253999357</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.007093425605536307</v>
+        <v>0.006365159128978215</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.00153898768809847</v>
+        <v>0.002017783857729172</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.00361809045226138</v>
+        <v>0.01119354838709682</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.00858131487889271</v>
+        <v>0.0099497487437186</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.002257728377909052</v>
+        <v>0.001477005706612966</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.01517587939698496</v>
+        <v>0.01858064516129038</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.003199718706047849</v>
+        <v>0.006331658291457265</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.009377162629757763</v>
+        <v>0.02140703517587939</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0003761969904240603</v>
+        <v>0.001338556970290594</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.001876046901172579</v>
+        <v>0.002393980848153243</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.002122114668652264</v>
+        <v>0.002311557788944729</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.000311418685121112</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.003161290322580623</v>
+        <v>0.004580645161290364</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.004254571026722942</v>
+        <v>0.00395309882747068</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.0001342732460556828</v>
+        <v>6.839945280439075e-05</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.001504787961696263</v>
+        <v>0.002129032258064578</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.002637130801687803</v>
+        <v>0.002177554438860962</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.003044982698961896</v>
+        <v>0.01093698987920343</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.001440536013400373</v>
+        <v>0.002222982216142311</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.01009677419354836</v>
+        <v>0.009304603330068606</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.01031668299053212</v>
+        <v>0.0102513875285668</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.004095334004699525</v>
+        <v>0.005582761998041174</v>
       </c>
     </row>
   </sheetData>
